--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443757</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443757</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443757</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443757</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,343 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127442781</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mellantomten, Mellantomten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>336025</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6608591</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128531628</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57679</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>335949</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6608641</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hörd</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128531713</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>336024</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6608571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127442781</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>128531628</v>
       </c>
       <c r="B4" t="n">
-        <v>57679</v>
+        <v>57683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127442781</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>128531628</v>
       </c>
       <c r="B4" t="n">
-        <v>57683</v>
+        <v>57710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127442781</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>128531628</v>
       </c>
       <c r="B4" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127442781</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>128531628</v>
       </c>
       <c r="B4" t="n">
-        <v>57714</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91529</v>
+        <v>91534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128531713</v>
       </c>
       <c r="B5" t="n">
-        <v>91534</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,116 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129836633</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>336047</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6608548</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack på granstubbe</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>129836633</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>129836633</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>129836633</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37401-2025 artfynd.xlsx
+++ b/artfynd/A 37401-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127443757</v>
+        <v>128531713</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,24 +708,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellantomten, Mellantomten, Vrm</t>
+          <t>Bråten, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>336041</v>
+        <v>336024</v>
       </c>
       <c r="R2" t="n">
-        <v>6608598</v>
+        <v>6608571</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,32 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127442781</v>
+        <v>128500968</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336025</v>
+        <v>335974</v>
       </c>
       <c r="R3" t="n">
-        <v>6608591</v>
+        <v>6608665</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På stor grov rönn</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Schulin</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Schulin</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128531628</v>
+        <v>127442781</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,45 +918,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråten, Vrm</t>
+          <t>Mellantomten, Mellantomten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335949</v>
+        <v>336025</v>
       </c>
       <c r="R4" t="n">
-        <v>6608641</v>
+        <v>6608591</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,27 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hörd</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128531713</v>
+        <v>127443757</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1041,22 +1037,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråten, Vrm</t>
+          <t>Mellantomten, Mellantomten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>336024</v>
+        <v>336041</v>
       </c>
       <c r="R5" t="n">
-        <v>6608571</v>
+        <v>6608598</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1078,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1102,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,11 +1123,11 @@
         <v>129836633</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1235,6 +1227,233 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128531628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>335949</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6608641</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hörd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129836632</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>336013</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6608544</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Knärot i/vid avverkningsanmält område. Kräver skyddszon med en radie på 50 meter.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
